--- a/database/excels/myservice/base-seeder.xlsx
+++ b/database/excels/myservice/base-seeder.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/monoland/Platform/monoland/database/excels/myservice/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{095178D8-C0E5-AA43-9007-630D0DA6AA02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61DAB9E8-1154-604F-ABB8-565DEAEDC5D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" activeTab="1" xr2:uid="{94E1010F-4E68-D749-BBCF-3803F804C4FE}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" activeTab="5" xr2:uid="{94E1010F-4E68-D749-BBCF-3803F804C4FE}"/>
   </bookViews>
   <sheets>
     <sheet name="module" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="80">
   <si>
     <t>name</t>
   </si>
@@ -116,9 +116,6 @@
     <t>Karpeg</t>
   </si>
   <si>
-    <t>Kenaikan Gaji Berkala</t>
-  </si>
-  <si>
     <t>Pensiun</t>
   </si>
   <si>
@@ -128,9 +125,6 @@
     <t>myservice-dashboard</t>
   </si>
   <si>
-    <t>myservice-vacation</t>
-  </si>
-  <si>
     <t>myservice-promotion</t>
   </si>
   <si>
@@ -140,9 +134,6 @@
     <t>myservice-personcard</t>
   </si>
   <si>
-    <t>myservice-increasing</t>
-  </si>
-  <si>
     <t>myservice-pension</t>
   </si>
   <si>
@@ -161,9 +152,6 @@
     <t>elderly</t>
   </si>
   <si>
-    <t>vacation</t>
-  </si>
-  <si>
     <t>promotion</t>
   </si>
   <si>
@@ -173,24 +161,15 @@
     <t>personcard</t>
   </si>
   <si>
-    <t>increasing</t>
-  </si>
-  <si>
     <t>pension</t>
   </si>
   <si>
-    <t>blue-grey</t>
-  </si>
-  <si>
     <t>Layanan Saya</t>
   </si>
   <si>
     <t>Layanan ASN</t>
   </si>
   <si>
-    <t>Ijin Perceraian</t>
-  </si>
-  <si>
     <t>myservice-divorce</t>
   </si>
   <si>
@@ -206,10 +185,91 @@
     <t>add_task</t>
   </si>
   <si>
-    <t>Pencantuman Gelar</t>
-  </si>
-  <si>
-    <t>myservice-inclusion</t>
+    <t>collections_bookmark</t>
+  </si>
+  <si>
+    <t>myservice-paidleave</t>
+  </si>
+  <si>
+    <t>K.G.B</t>
+  </si>
+  <si>
+    <t>paidleave</t>
+  </si>
+  <si>
+    <t>payincrease</t>
+  </si>
+  <si>
+    <t>myservice-payincrease</t>
+  </si>
+  <si>
+    <t>brown</t>
+  </si>
+  <si>
+    <t>Laporan Pernikahan</t>
+  </si>
+  <si>
+    <t>Laporan Kelahiran Anak</t>
+  </si>
+  <si>
+    <t>myservice-marriage</t>
+  </si>
+  <si>
+    <t>Izin Perceraian</t>
+  </si>
+  <si>
+    <t>myservice-birth</t>
+  </si>
+  <si>
+    <t>marriage</t>
+  </si>
+  <si>
+    <t>birth</t>
+  </si>
+  <si>
+    <t>local_florist</t>
+  </si>
+  <si>
+    <t>myservice-death</t>
+  </si>
+  <si>
+    <t>death</t>
+  </si>
+  <si>
+    <t>baby_changing_station</t>
+  </si>
+  <si>
+    <t>toys</t>
+  </si>
+  <si>
+    <t>Laporan Kematian Keluarga</t>
+  </si>
+  <si>
+    <t>Usulan Pindah Unker</t>
+  </si>
+  <si>
+    <t>myservice-swith</t>
+  </si>
+  <si>
+    <t>swith</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>cameraswitch</t>
+  </si>
+  <si>
+    <t>Diklat</t>
+  </si>
+  <si>
+    <t>Pendidikan dan Latihan</t>
+  </si>
+  <si>
+    <t>myservice-training</t>
+  </si>
+  <si>
+    <t>training</t>
   </si>
 </sst>
 </file>
@@ -618,25 +678,25 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E2" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -646,19 +706,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CF7F25A-0145-E049-BABB-6C723A859E1D}">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="27.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="51.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="10.83203125" style="4"/>
-    <col min="9" max="9" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5" customWidth="1"/>
+    <col min="4" max="4" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="51.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="10.83203125" style="4"/>
+    <col min="10" max="10" width="16.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -666,244 +727,402 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" t="s">
-        <v>31</v>
-      </c>
       <c r="D2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
-        <v>30</v>
-      </c>
       <c r="F2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="4" t="b">
+      <c r="H2" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="H2" s="4" t="b">
+      <c r="I2" s="4" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G3" s="4" t="b">
+        <v>29</v>
+      </c>
+      <c r="G3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H3" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="H3" s="4" t="b">
+      <c r="I3" s="4" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" s="4" t="b">
+        <v>29</v>
+      </c>
+      <c r="G4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H4" s="4" t="b">
+      <c r="I4" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" t="s">
         <v>41</v>
       </c>
-      <c r="E5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" t="s">
-        <v>45</v>
-      </c>
-      <c r="G5" s="4" t="b">
+      <c r="H5" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H5" s="4" t="b">
+      <c r="I5" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" t="s">
+        <v>79</v>
+      </c>
+      <c r="H9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" t="s">
         <v>46</v>
       </c>
-      <c r="G6" s="4" t="b">
+      <c r="E10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="H6" s="4" t="b">
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" t="s">
+        <v>63</v>
+      </c>
+      <c r="H11" s="4" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7" s="4" t="b">
+      <c r="I11" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" t="s">
+        <v>64</v>
+      </c>
+      <c r="H12" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H7" s="4" t="b">
+      <c r="I12" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" t="s">
-        <v>48</v>
-      </c>
-      <c r="G8" s="4" t="b">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" t="s">
+        <v>66</v>
+      </c>
+      <c r="E13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" t="s">
+        <v>67</v>
+      </c>
+      <c r="H13" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="H8" s="4" t="b">
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" t="s">
+        <v>71</v>
+      </c>
+      <c r="D14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" t="s">
+        <v>73</v>
+      </c>
+      <c r="H14" s="4" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H9" s="4" t="b">
+      <c r="I14" s="4" t="b">
         <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -913,7 +1132,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{462F859E-7489-7142-8B02-E1AE063A22DB}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="22.33203125" bestFit="1" customWidth="1"/>
@@ -933,10 +1152,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
         <v>30</v>
-      </c>
-      <c r="B2" t="s">
-        <v>31</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>15</v>
@@ -944,10 +1163,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
         <v>23</v>
@@ -955,10 +1174,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
         <v>23</v>
@@ -966,10 +1185,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
         <v>23</v>
@@ -977,10 +1196,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
         <v>23</v>
@@ -988,10 +1207,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
         <v>23</v>
@@ -999,10 +1218,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
         <v>23</v>
@@ -1010,12 +1229,67 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1043,7 +1317,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -1051,7 +1325,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
@@ -1064,7 +1338,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{279D8F2B-ACF8-DF40-AE6A-EC20C786574F}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="33.33203125" customWidth="1"/>
@@ -1084,90 +1358,145 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
         <v>30</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
         <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
         <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1177,7 +1506,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2E44C3F-3A12-F647-BCB1-FF7A86E9DA05}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="33.33203125" customWidth="1"/>
@@ -1200,13 +1529,13 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
         <v>30</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>31</v>
       </c>
       <c r="D2" t="s">
         <v>17</v>
@@ -1214,13 +1543,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
         <v>17</v>
@@ -1228,13 +1557,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
         <v>17</v>
@@ -1242,13 +1571,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
         <v>17</v>
@@ -1256,13 +1585,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
@@ -1270,13 +1599,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
         <v>17</v>
@@ -1284,13 +1613,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
         <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
         <v>17</v>
@@ -1298,15 +1627,85 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
         <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" t="s">
         <v>17</v>
       </c>
     </row>

--- a/database/excels/myservice/base-seeder.xlsx
+++ b/database/excels/myservice/base-seeder.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/monoland/Platform/monoland/database/excels/myservice/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61DAB9E8-1154-604F-ABB8-565DEAEDC5D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{923E8692-72C0-5F4F-BA91-2628206A773F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" activeTab="5" xr2:uid="{94E1010F-4E68-D749-BBCF-3803F804C4FE}"/>
+    <workbookView xWindow="2520" yWindow="500" windowWidth="33600" windowHeight="20500" activeTab="1" xr2:uid="{94E1010F-4E68-D749-BBCF-3803F804C4FE}"/>
   </bookViews>
   <sheets>
     <sheet name="module" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="95">
   <si>
     <t>name</t>
   </si>
@@ -206,9 +206,6 @@
     <t>brown</t>
   </si>
   <si>
-    <t>Laporan Pernikahan</t>
-  </si>
-  <si>
     <t>Laporan Kelahiran Anak</t>
   </si>
   <si>
@@ -270,6 +267,54 @@
   </si>
   <si>
     <t>training</t>
+  </si>
+  <si>
+    <t>Izin Pernikahan</t>
+  </si>
+  <si>
+    <t>Kelahiran Anak</t>
+  </si>
+  <si>
+    <t>Kematian Keluarga</t>
+  </si>
+  <si>
+    <t>Halo BKD</t>
+  </si>
+  <si>
+    <t>myservice-consultation</t>
+  </si>
+  <si>
+    <t>perm_phone_msg</t>
+  </si>
+  <si>
+    <t>consultation</t>
+  </si>
+  <si>
+    <t>Izin Belajar</t>
+  </si>
+  <si>
+    <t>Banding Kinerja</t>
+  </si>
+  <si>
+    <t>Banding Capaian Kinerja</t>
+  </si>
+  <si>
+    <t>myservice-performance</t>
+  </si>
+  <si>
+    <t>myservice-study</t>
+  </si>
+  <si>
+    <t>history_edu</t>
+  </si>
+  <si>
+    <t>speed</t>
+  </si>
+  <si>
+    <t>study</t>
+  </si>
+  <si>
+    <t>performance</t>
   </si>
 </sst>
 </file>
@@ -706,7 +751,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CF7F25A-0145-E049-BABB-6C723A859E1D}">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="27.5" bestFit="1" customWidth="1"/>
@@ -727,7 +772,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
@@ -956,13 +1001,13 @@
         <v>29</v>
       </c>
       <c r="B9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" t="s">
         <v>76</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>77</v>
-      </c>
-      <c r="D9" t="s">
-        <v>78</v>
       </c>
       <c r="E9" t="s">
         <v>51</v>
@@ -971,7 +1016,7 @@
         <v>29</v>
       </c>
       <c r="G9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H9" s="4" t="b">
         <v>0</v>
@@ -985,10 +1030,10 @@
         <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D10" t="s">
         <v>46</v>
@@ -1014,22 +1059,22 @@
         <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F11" t="s">
         <v>29</v>
       </c>
       <c r="G11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H11" s="4" t="b">
         <v>0</v>
@@ -1043,22 +1088,22 @@
         <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F12" t="s">
         <v>29</v>
       </c>
       <c r="G12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H12" s="4" t="b">
         <v>0</v>
@@ -1072,22 +1117,22 @@
         <v>29</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" t="s">
         <v>66</v>
-      </c>
-      <c r="E13" t="s">
-        <v>69</v>
-      </c>
-      <c r="F13" t="s">
-        <v>29</v>
-      </c>
-      <c r="G13" t="s">
-        <v>67</v>
       </c>
       <c r="H13" s="4" t="b">
         <v>0</v>
@@ -1101,27 +1146,114 @@
         <v>29</v>
       </c>
       <c r="B14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" t="s">
         <v>71</v>
       </c>
-      <c r="C14" t="s">
-        <v>71</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" t="s">
         <v>72</v>
-      </c>
-      <c r="E14" t="s">
-        <v>75</v>
-      </c>
-      <c r="F14" t="s">
-        <v>29</v>
-      </c>
-      <c r="G14" t="s">
-        <v>73</v>
       </c>
       <c r="H14" s="4" t="b">
         <v>0</v>
       </c>
       <c r="I14" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" t="s">
+        <v>83</v>
+      </c>
+      <c r="E15" t="s">
+        <v>84</v>
+      </c>
+      <c r="F15" t="s">
+        <v>29</v>
+      </c>
+      <c r="G15" t="s">
+        <v>85</v>
+      </c>
+      <c r="H15" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" t="s">
+        <v>86</v>
+      </c>
+      <c r="D16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E16" t="s">
+        <v>91</v>
+      </c>
+      <c r="F16" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" t="s">
+        <v>93</v>
+      </c>
+      <c r="H16" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17" t="s">
+        <v>89</v>
+      </c>
+      <c r="E17" t="s">
+        <v>92</v>
+      </c>
+      <c r="F17" t="s">
+        <v>29</v>
+      </c>
+      <c r="G17" t="s">
+        <v>94</v>
+      </c>
+      <c r="H17" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1132,7 +1264,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{462F859E-7489-7142-8B02-E1AE063A22DB}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="22.33203125" bestFit="1" customWidth="1"/>
@@ -1232,7 +1364,7 @@
         <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
         <v>23</v>
@@ -1254,7 +1386,7 @@
         <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
         <v>23</v>
@@ -1265,7 +1397,7 @@
         <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
         <v>23</v>
@@ -1276,7 +1408,7 @@
         <v>29</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
         <v>23</v>
@@ -1287,9 +1419,42 @@
         <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1338,7 +1503,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{279D8F2B-ACF8-DF40-AE6A-EC20C786574F}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="33.33203125" customWidth="1"/>
@@ -1441,7 +1606,7 @@
         <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1463,7 +1628,7 @@
         <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -1474,7 +1639,7 @@
         <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1485,7 +1650,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1496,7 +1661,40 @@
         <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1506,7 +1704,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2E44C3F-3A12-F647-BCB1-FF7A86E9DA05}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="33.33203125" customWidth="1"/>
@@ -1633,7 +1831,7 @@
         <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
         <v>17</v>
@@ -1661,7 +1859,7 @@
         <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D11" t="s">
         <v>17</v>
@@ -1675,7 +1873,7 @@
         <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D12" t="s">
         <v>17</v>
@@ -1689,7 +1887,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D13" t="s">
         <v>17</v>
@@ -1703,9 +1901,51 @@
         <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" t="s">
         <v>17</v>
       </c>
     </row>
